--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T14:55:17+00:00</t>
+    <t>2023-12-11T15:07:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Observation de la taille</t>
+    <t>Profil de la ressource Observation pour définir une taille</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T15:07:49+00:00</t>
+    <t>2023-12-11T15:09:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T15:09:19+00:00</t>
+    <t>2023-12-11T15:13:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T15:13:34+00:00</t>
+    <t>2023-12-11T15:58:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T15:58:18+00:00</t>
+    <t>2023-12-11T16:02:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T16:02:47+00:00</t>
+    <t>2023-12-11T17:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T17:03:26+00:00</t>
+    <t>2023-12-12T13:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T13:44:55+00:00</t>
+    <t>2023-12-12T13:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T13:59:44+00:00</t>
+    <t>2023-12-12T14:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T14:34:19+00:00</t>
+    <t>2023-12-12T16:43:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/nr-add-nos-generate-profil-table/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T16:43:39+00:00</t>
+    <t>2023-12-13T09:56:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
